--- a/files/港岛-鲗鱼涌-君豪峰.xlsx
+++ b/files/港岛-鲗鱼涌-君豪峰.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="君豪峰 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="君豪峰" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -170,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,19 +213,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,10 +231,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -598,7 +636,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -22021,193 +22059,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>君豪峰 - 君豪峰 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>君豪峰 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>464 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>9 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>455 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>464</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>455</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L4" s="19" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M4" s="19" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N4" s="19" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O4" s="19" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P4" s="19" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q4" s="19" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $711万
@@ -22215,7 +22253,7 @@
 (20年-05月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $897万
@@ -22223,7 +22261,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $919万
@@ -22231,7 +22269,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $868万
@@ -22239,7 +22277,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 299呎 (1房)
 $916万
@@ -22247,15 +22285,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,221万
+$1221万
 $27,066/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $784万
@@ -22263,7 +22301,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $820万
@@ -22271,7 +22309,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $626万
@@ -22279,7 +22317,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K6" s="16" t="inlineStr">
+      <c r="K5" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $866万
@@ -22287,7 +22325,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L6" s="16" t="inlineStr">
+      <c r="L5" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $838万
@@ -22295,7 +22333,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M6" s="16" t="inlineStr">
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $643万
@@ -22303,7 +22341,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N6" s="16" t="inlineStr">
+      <c r="N5" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $641万
@@ -22311,7 +22349,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O6" s="16" t="inlineStr">
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $736万
@@ -22319,7 +22357,7 @@
 (19年-02月)</t>
         </is>
       </c>
-      <c r="P6" s="16" t="inlineStr">
+      <c r="P5" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $882万
@@ -22327,7 +22365,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q6" s="16" t="inlineStr">
+      <c r="Q5" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $722万
@@ -22336,13 +22374,13 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $706万
@@ -22350,7 +22388,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $871万
@@ -22358,7 +22396,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $884万
@@ -22366,7 +22404,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $843万
@@ -22374,7 +22412,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $890万
@@ -22382,15 +22420,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,210万
+$1210万
 $26,833/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $804万
@@ -22398,7 +22436,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $816万
@@ -22406,7 +22444,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 218呎 (开放式)
 $616万
@@ -22414,7 +22452,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K7" s="16" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $835万
@@ -22422,7 +22460,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L7" s="16" t="inlineStr">
+      <c r="L6" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $809万
@@ -22430,7 +22468,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M7" s="16" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $614万
@@ -22438,7 +22476,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N7" s="16" t="inlineStr">
+      <c r="N6" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $618万
@@ -22446,15 +22484,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O7" s="16" t="inlineStr">
+      <c r="O6" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
-$1,082万
+$1082万
 $28,190/呎
 (已售)</t>
         </is>
       </c>
-      <c r="P7" s="16" t="inlineStr">
+      <c r="P6" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $872万
@@ -22462,7 +22500,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q7" s="16" t="inlineStr">
+      <c r="Q6" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $716万
@@ -22471,13 +22509,13 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $697万
@@ -22485,7 +22523,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $869万
@@ -22493,7 +22531,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $891万
@@ -22501,7 +22539,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $793万
@@ -22509,7 +22547,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $870万
@@ -22517,15 +22555,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,199万
+$1199万
 $26,576/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $764万
@@ -22533,7 +22571,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $799万
@@ -22541,7 +22579,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $623万
@@ -22549,7 +22587,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K8" s="16" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $811万
@@ -22557,7 +22595,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L8" s="16" t="inlineStr">
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $801万
@@ -22565,7 +22603,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M8" s="16" t="inlineStr">
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $614万
@@ -22573,7 +22611,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N8" s="16" t="inlineStr">
+      <c r="N7" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $618万
@@ -22581,15 +22619,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O8" s="16" t="inlineStr">
+      <c r="O7" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
-$1,061万
+$1061万
 $27,629/呎
 (已售)</t>
         </is>
       </c>
-      <c r="P8" s="16" t="inlineStr">
+      <c r="P7" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $867万
@@ -22597,7 +22635,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q8" s="16" t="inlineStr">
+      <c r="Q7" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $720万
@@ -22606,13 +22644,13 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $688万
@@ -22620,7 +22658,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $849万
@@ -22628,7 +22666,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $862万
@@ -22636,7 +22674,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $814万
@@ -22644,7 +22682,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 299呎 (1房)
 $868万
@@ -22652,15 +22690,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,187万
+$1187万
 $26,318/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $756万
@@ -22668,7 +22706,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $783万
@@ -22676,7 +22714,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $611万
@@ -22684,7 +22722,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K9" s="16" t="inlineStr">
+      <c r="K8" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $803万
@@ -22692,7 +22730,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="L8" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $793万
@@ -22700,7 +22738,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M9" s="16" t="inlineStr">
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $608万
@@ -22708,7 +22746,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N9" s="16" t="inlineStr">
+      <c r="N8" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $606万
@@ -22716,7 +22754,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O9" s="16" t="inlineStr">
+      <c r="O8" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $776万
@@ -22724,7 +22762,7 @@
 (19年-03月)</t>
         </is>
       </c>
-      <c r="P9" s="16" t="inlineStr">
+      <c r="P8" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $862万
@@ -22732,7 +22770,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q9" s="16" t="inlineStr">
+      <c r="Q8" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $724万
@@ -22741,13 +22779,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $675万
@@ -22755,7 +22793,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $841万
@@ -22763,7 +22801,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $853万
@@ -22771,7 +22809,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $823万
@@ -22779,7 +22817,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $851万
@@ -22787,15 +22825,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,108万
+$1108万
 $24,579/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $751万
@@ -22803,7 +22841,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $786万
@@ -22811,7 +22849,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $601万
@@ -22819,7 +22857,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K10" s="16" t="inlineStr">
+      <c r="K9" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $798万
@@ -22827,7 +22865,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L10" s="16" t="inlineStr">
+      <c r="L9" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $796万
@@ -22835,7 +22873,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M10" s="16" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $611万
@@ -22843,7 +22881,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N10" s="16" t="inlineStr">
+      <c r="N9" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $609万
@@ -22851,15 +22889,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O10" s="16" t="inlineStr">
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
-$1,065万
+$1065万
 $27,726/呎
 (已售)</t>
         </is>
       </c>
-      <c r="P10" s="16" t="inlineStr">
+      <c r="P9" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $866万
@@ -22867,7 +22905,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q10" s="17" t="inlineStr">
+      <c r="Q9" s="21" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $639万
@@ -22876,13 +22914,13 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $668万
@@ -22890,7 +22928,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $841万
@@ -22898,7 +22936,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $845万
@@ -22906,7 +22944,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $815万
@@ -22914,7 +22952,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $852万
@@ -22922,15 +22960,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,171万
+$1171万
 $25,973/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $746万
@@ -22938,7 +22976,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $781万
@@ -22946,7 +22984,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $569万
@@ -22954,7 +22992,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K11" s="16" t="inlineStr">
+      <c r="K10" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $801万
@@ -22962,7 +23000,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L11" s="16" t="inlineStr">
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $782万
@@ -22970,7 +23008,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M11" s="16" t="inlineStr">
+      <c r="M10" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $600万
@@ -22978,7 +23016,7 @@
 (18年-06月)</t>
         </is>
       </c>
-      <c r="N11" s="16" t="inlineStr">
+      <c r="N10" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $598万
@@ -22986,15 +23024,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O11" s="16" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
-$1,088万
+$1088万
 $28,344/呎
 (19年-02月)</t>
         </is>
       </c>
-      <c r="P11" s="16" t="inlineStr">
+      <c r="P10" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $852万
@@ -23002,7 +23040,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q11" s="17" t="inlineStr">
+      <c r="Q10" s="21" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $636万
@@ -23011,13 +23049,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $669万
@@ -23025,7 +23063,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $824万
@@ -23033,7 +23071,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $837万
@@ -23041,7 +23079,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $799万
@@ -23049,7 +23087,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $844万
@@ -23057,15 +23095,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,151万
+$1151万
 $25,530/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $827万
@@ -23073,7 +23111,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $776万
@@ -23081,7 +23119,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $593万
@@ -23089,7 +23127,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K12" s="16" t="inlineStr">
+      <c r="K11" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $796万
@@ -23097,7 +23135,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L12" s="16" t="inlineStr">
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $785万
@@ -23105,7 +23143,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M12" s="16" t="inlineStr">
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $573万
@@ -23113,7 +23151,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N12" s="16" t="inlineStr">
+      <c r="N11" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $601万
@@ -23121,15 +23159,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O12" s="16" t="inlineStr">
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
-$1,041万
+$1041万
 $27,105/呎
 (已售)</t>
         </is>
       </c>
-      <c r="P12" s="16" t="inlineStr">
+      <c r="P11" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $844万
@@ -23137,7 +23175,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q12" s="17" t="inlineStr">
+      <c r="Q11" s="21" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $630万
@@ -23146,13 +23184,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $662万
@@ -23160,7 +23198,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $825万
@@ -23168,7 +23206,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $829万
@@ -23176,7 +23214,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $753万
@@ -23184,7 +23222,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $796万
@@ -23192,15 +23230,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,168万
+$1168万
 $25,893/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $813万
@@ -23208,7 +23246,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $763万
@@ -23216,7 +23254,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $567万
@@ -23224,7 +23262,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K13" s="16" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $791万
@@ -23232,7 +23270,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="L12" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $772万
@@ -23240,7 +23278,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M13" s="16" t="inlineStr">
+      <c r="M12" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $587万
@@ -23248,7 +23286,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N13" s="16" t="inlineStr">
+      <c r="N12" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $609万
@@ -23256,15 +23294,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O13" s="16" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
-$1,034万
+$1034万
 $26,925/呎
 (已售)</t>
         </is>
       </c>
-      <c r="P13" s="16" t="inlineStr">
+      <c r="P12" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $844万
@@ -23272,7 +23310,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q13" s="16" t="inlineStr">
+      <c r="Q12" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $689万
@@ -23281,13 +23319,13 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $655万
@@ -23295,7 +23333,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $808万
@@ -23303,7 +23341,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $820万
@@ -23311,7 +23349,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $799万
@@ -23319,7 +23357,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 299呎 (1房)
 $836万
@@ -23327,15 +23365,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,148万
+$1148万
 $25,454/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $808万
@@ -23343,7 +23381,7 @@
 (20年-03月)</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $766万
@@ -23351,7 +23389,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $586万
@@ -23359,7 +23397,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K14" s="16" t="inlineStr">
+      <c r="K13" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $794万
@@ -23367,7 +23405,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L14" s="16" t="inlineStr">
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $767万
@@ -23375,7 +23413,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M14" s="16" t="inlineStr">
+      <c r="M13" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $583万
@@ -23383,7 +23421,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N14" s="16" t="inlineStr">
+      <c r="N13" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $605万
@@ -23391,15 +23429,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O14" s="16" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
-$1,048万
+$1048万
 $27,280/呎
 (已售)</t>
         </is>
       </c>
-      <c r="P14" s="16" t="inlineStr">
+      <c r="P13" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $836万
@@ -23407,7 +23445,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q14" s="16" t="inlineStr">
+      <c r="Q13" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $696万
@@ -23416,13 +23454,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $664万
@@ -23430,7 +23468,7 @@
 (19年-07月)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $811万
@@ -23438,7 +23476,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $823万
@@ -23446,7 +23484,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $778万
@@ -23454,7 +23492,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $813万
@@ -23462,15 +23500,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,075万
+$1075万
 $23,828/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $811万
@@ -23478,7 +23516,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $753万
@@ -23486,7 +23524,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 218呎 (开放式)
 $560万
@@ -23494,7 +23532,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K15" s="16" t="inlineStr">
+      <c r="K14" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $772万
@@ -23502,7 +23540,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L15" s="16" t="inlineStr">
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $785万
@@ -23510,7 +23548,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M15" s="16" t="inlineStr">
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $562万
@@ -23518,7 +23556,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N15" s="16" t="inlineStr">
+      <c r="N14" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $583万
@@ -23526,15 +23564,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O15" s="16" t="inlineStr">
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
-$1,009万
+$1009万
 $26,288/呎
 (已售)</t>
         </is>
       </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="P14" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $822万
@@ -23542,7 +23580,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q15" s="16" t="inlineStr">
+      <c r="Q14" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $685万
@@ -23551,13 +23589,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $647万
@@ -23565,7 +23603,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $797万
@@ -23573,7 +23611,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $809万
@@ -23581,7 +23619,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $728万
@@ -23589,7 +23627,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 299呎 (1房)
 $816万
@@ -23597,15 +23635,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,121万
+$1121万
 $24,850/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $805万
@@ -23613,7 +23651,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $747万
@@ -23621,7 +23659,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 218呎 (开放式)
 $562万
@@ -23629,7 +23667,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K16" s="16" t="inlineStr">
+      <c r="K15" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $775万
@@ -23637,7 +23675,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L16" s="16" t="inlineStr">
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $756万
@@ -23645,7 +23683,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M16" s="16" t="inlineStr">
+      <c r="M15" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $564万
@@ -23653,7 +23691,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N16" s="16" t="inlineStr">
+      <c r="N15" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $585万
@@ -23661,15 +23699,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O16" s="16" t="inlineStr">
+      <c r="O15" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
-$1,013万
+$1013万
 $26,385/呎
 (已售)</t>
         </is>
       </c>
-      <c r="P16" s="16" t="inlineStr">
+      <c r="P15" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $816万
@@ -23677,7 +23715,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q16" s="16" t="inlineStr">
+      <c r="Q15" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $673万
@@ -23686,13 +23724,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $642万
@@ -23700,7 +23738,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $800万
@@ -23708,7 +23746,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $804万
@@ -23716,7 +23754,7 @@
 (19年-06月)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $731万
@@ -23724,7 +23762,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 299呎 (1房)
 $803万
@@ -23732,15 +23770,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,125万
+$1125万
 $24,939/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $791万
@@ -23748,7 +23786,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $750万
@@ -23756,7 +23794,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $552万
@@ -23764,7 +23802,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K17" s="16" t="inlineStr">
+      <c r="K16" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $770万
@@ -23772,7 +23810,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L17" s="16" t="inlineStr">
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $759万
@@ -23780,7 +23818,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M17" s="16" t="inlineStr">
+      <c r="M16" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $560万
@@ -23788,7 +23826,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N17" s="16" t="inlineStr">
+      <c r="N16" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $575万
@@ -23796,15 +23834,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O17" s="16" t="inlineStr">
+      <c r="O16" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
-$1,027万
+$1027万
 $26,748/呎
 (已售)</t>
         </is>
       </c>
-      <c r="P17" s="16" t="inlineStr">
+      <c r="P16" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $819万
@@ -23812,7 +23850,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q17" s="16" t="inlineStr">
+      <c r="Q16" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $669万
@@ -23821,13 +23859,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $645万
@@ -23835,7 +23873,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $786万
@@ -23843,7 +23881,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $798万
@@ -23851,7 +23889,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $718万
@@ -23859,7 +23897,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $806万
@@ -23867,15 +23905,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,117万
+$1117万
 $24,766/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $794万
@@ -23883,7 +23921,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $745万
@@ -23891,7 +23929,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $543万
@@ -23899,7 +23937,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K18" s="16" t="inlineStr">
+      <c r="K17" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $780万
@@ -23907,7 +23945,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L18" s="16" t="inlineStr">
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $746万
@@ -23915,7 +23953,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M18" s="16" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $562万
@@ -23923,7 +23961,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N18" s="16" t="inlineStr">
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $577万
@@ -23931,7 +23969,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O18" s="16" t="inlineStr">
+      <c r="O17" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $999万
@@ -23939,7 +23977,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P18" s="16" t="inlineStr">
+      <c r="P17" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $808万
@@ -23947,7 +23985,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q18" s="16" t="inlineStr">
+      <c r="Q17" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $660万
@@ -23956,13 +23994,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $634万
@@ -23970,7 +24008,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $789万
@@ -23978,7 +24016,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $801万
@@ -23986,7 +24024,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $713万
@@ -23994,7 +24032,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $762万
@@ -24002,15 +24040,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,045万
+$1045万
 $23,179/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $789万
@@ -24018,7 +24056,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $740万
@@ -24026,7 +24064,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $551万
@@ -24034,7 +24072,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K19" s="16" t="inlineStr">
+      <c r="K18" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $775万
@@ -24042,7 +24080,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L19" s="16" t="inlineStr">
+      <c r="L18" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $756万
@@ -24050,7 +24088,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M19" s="16" t="inlineStr">
+      <c r="M18" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $547万
@@ -24058,7 +24096,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N19" s="16" t="inlineStr">
+      <c r="N18" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $579万
@@ -24066,7 +24104,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O19" s="16" t="inlineStr">
+      <c r="O18" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $945万
@@ -24074,7 +24112,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P19" s="16" t="inlineStr">
+      <c r="P18" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $789万
@@ -24082,7 +24120,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q19" s="16" t="inlineStr">
+      <c r="Q18" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $651万
@@ -24091,13 +24129,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $629万
@@ -24105,7 +24143,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $783万
@@ -24113,7 +24151,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $787万
@@ -24121,7 +24159,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $716万
@@ -24129,7 +24167,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $757万
@@ -24137,15 +24175,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,038万
+$1038万
 $23,015/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $783万
@@ -24153,7 +24191,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $750万
@@ -24161,7 +24199,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 218呎 (开放式)
 $536万
@@ -24169,7 +24207,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K20" s="16" t="inlineStr">
+      <c r="K19" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $746万
@@ -24177,7 +24215,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L20" s="16" t="inlineStr">
+      <c r="L19" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $743万
@@ -24185,7 +24223,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M20" s="16" t="inlineStr">
+      <c r="M19" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $548万
@@ -24193,7 +24231,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N20" s="16" t="inlineStr">
+      <c r="N19" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $563万
@@ -24201,7 +24239,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O20" s="16" t="inlineStr">
+      <c r="O19" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $985万
@@ -24209,7 +24247,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P20" s="16" t="inlineStr">
+      <c r="P19" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $791万
@@ -24217,7 +24255,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q20" s="16" t="inlineStr">
+      <c r="Q19" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $646万
@@ -24226,13 +24264,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $625万
@@ -24240,7 +24278,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $778万
@@ -24248,7 +24286,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $782万
@@ -24256,7 +24294,7 @@
 (19年-05月)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $725万
@@ -24264,7 +24302,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $752万
@@ -24272,15 +24310,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,063万
+$1063万
 $23,574/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $777万
@@ -24288,7 +24326,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $687万
@@ -24296,7 +24334,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $538万
@@ -24304,7 +24342,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K21" s="16" t="inlineStr">
+      <c r="K20" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $749万
@@ -24312,7 +24350,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L21" s="16" t="inlineStr">
+      <c r="L20" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $738万
@@ -24320,7 +24358,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M21" s="16" t="inlineStr">
+      <c r="M20" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $545万
@@ -24328,7 +24366,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N21" s="16" t="inlineStr">
+      <c r="N20" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $565万
@@ -24336,7 +24374,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O21" s="16" t="inlineStr">
+      <c r="O20" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $968万
@@ -24344,7 +24382,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P21" s="16" t="inlineStr">
+      <c r="P20" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $786万
@@ -24352,7 +24390,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q21" s="16" t="inlineStr">
+      <c r="Q20" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $648万
@@ -24361,13 +24399,13 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $616万
@@ -24375,7 +24413,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $775万
@@ -24383,7 +24421,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $787万
@@ -24391,7 +24429,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $701万
@@ -24399,7 +24437,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $778万
@@ -24407,15 +24445,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,038万
+$1038万
 $23,012/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $767万
@@ -24423,7 +24461,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $692万
@@ -24431,7 +24469,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 218呎 (开放式)
 $541万
@@ -24439,7 +24477,7 @@
 (17年-12月)</t>
         </is>
       </c>
-      <c r="K22" s="16" t="inlineStr">
+      <c r="K21" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $746万
@@ -24447,7 +24485,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L22" s="16" t="inlineStr">
+      <c r="L21" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $735万
@@ -24455,7 +24493,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M22" s="16" t="inlineStr">
+      <c r="M21" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $537万
@@ -24463,7 +24501,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N22" s="16" t="inlineStr">
+      <c r="N21" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $564万
@@ -24471,7 +24509,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O22" s="16" t="inlineStr">
+      <c r="O21" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $948万
@@ -24479,7 +24517,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P22" s="16" t="inlineStr">
+      <c r="P21" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $775万
@@ -24487,7 +24525,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q22" s="16" t="inlineStr">
+      <c r="Q21" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $639万
@@ -24496,13 +24534,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $612万
@@ -24510,7 +24548,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $769万
@@ -24518,7 +24556,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $782万
@@ -24526,7 +24564,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $703万
@@ -24534,7 +24572,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $744万
@@ -24542,15 +24580,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,030万
+$1030万
 $22,848/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $761万
@@ -24558,7 +24596,7 @@
 (19年-05月)</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $680万
@@ -24566,7 +24604,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $532万
@@ -24574,7 +24612,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K23" s="16" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $733万
@@ -24582,7 +24620,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L23" s="16" t="inlineStr">
+      <c r="L22" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $730万
@@ -24590,7 +24628,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M23" s="16" t="inlineStr">
+      <c r="M22" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $539万
@@ -24598,7 +24636,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N23" s="16" t="inlineStr">
+      <c r="N22" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $554万
@@ -24606,7 +24644,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O23" s="16" t="inlineStr">
+      <c r="O22" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $968万
@@ -24614,7 +24652,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P23" s="16" t="inlineStr">
+      <c r="P22" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $769万
@@ -24622,7 +24660,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q23" s="16" t="inlineStr">
+      <c r="Q22" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $642万
@@ -24631,13 +24669,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $614万
@@ -24645,7 +24683,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $756万
@@ -24653,7 +24691,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $776万
@@ -24661,7 +24699,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $705万
@@ -24669,7 +24707,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $776万
@@ -24677,15 +24715,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,023万
+$1023万
 $22,685/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $764万
@@ -24693,7 +24731,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $682万
@@ -24701,7 +24739,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 218呎 (开放式)
 $523万
@@ -24709,7 +24747,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K24" s="16" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $728万
@@ -24717,7 +24755,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L24" s="16" t="inlineStr">
+      <c r="L23" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $724万
@@ -24725,7 +24763,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M24" s="16" t="inlineStr">
+      <c r="M23" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $535万
@@ -24733,7 +24771,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N24" s="16" t="inlineStr">
+      <c r="N23" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $550万
@@ -24741,7 +24779,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O24" s="16" t="inlineStr">
+      <c r="O23" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $961万
@@ -24749,7 +24787,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P24" s="16" t="inlineStr">
+      <c r="P23" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $769万
@@ -24757,7 +24795,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q24" s="16" t="inlineStr">
+      <c r="Q23" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $628万
@@ -24766,13 +24804,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $599万
@@ -24780,7 +24818,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $745万
@@ -24788,7 +24826,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $765万
@@ -24796,7 +24834,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $688万
@@ -24804,7 +24842,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 299呎 (1房)
 $765万
@@ -24812,15 +24850,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,016万
+$1016万
 $22,518/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $758万
@@ -24828,7 +24866,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $677万
@@ -24836,7 +24874,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $530万
@@ -24844,7 +24882,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K25" s="16" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $723万
@@ -24852,7 +24890,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L25" s="16" t="inlineStr">
+      <c r="L24" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $719万
@@ -24860,7 +24898,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M25" s="16" t="inlineStr">
+      <c r="M24" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $526万
@@ -24868,7 +24906,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N25" s="16" t="inlineStr">
+      <c r="N24" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $552万
@@ -24876,7 +24914,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O25" s="16" t="inlineStr">
+      <c r="O24" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $909万
@@ -24884,7 +24922,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P25" s="16" t="inlineStr">
+      <c r="P24" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $739万
@@ -24892,7 +24930,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q25" s="16" t="inlineStr">
+      <c r="Q24" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $617万
@@ -24901,13 +24939,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $590万
@@ -24915,7 +24953,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $734万
@@ -24923,7 +24961,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $754万
@@ -24931,7 +24969,7 @@
 (19年-05月)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $722万
@@ -24939,7 +24977,7 @@
 (18年-07月)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $756万
@@ -24947,15 +24985,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,008万
+$1008万
 $22,355/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $745万
@@ -24963,7 +25001,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $665万
@@ -24971,7 +25009,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $521万
@@ -24979,7 +25017,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K26" s="16" t="inlineStr">
+      <c r="K25" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $725万
@@ -24987,7 +25025,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L26" s="16" t="inlineStr">
+      <c r="L25" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $714万
@@ -24995,7 +25033,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M26" s="16" t="inlineStr">
+      <c r="M25" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $527万
@@ -25003,7 +25041,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N26" s="16" t="inlineStr">
+      <c r="N25" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $548万
@@ -25011,7 +25049,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O26" s="16" t="inlineStr">
+      <c r="O25" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $947万
@@ -25019,7 +25057,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P26" s="16" t="inlineStr">
+      <c r="P25" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $725万
@@ -25027,7 +25065,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q26" s="16" t="inlineStr">
+      <c r="Q25" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $592万
@@ -25036,13 +25074,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $594万
@@ -25050,7 +25088,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $723万
@@ -25058,7 +25096,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $743万
@@ -25066,7 +25104,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $709万
@@ -25074,7 +25112,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $759万
@@ -25082,15 +25120,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,040万
+$1040万
 $23,057/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $747万
@@ -25098,7 +25136,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $681万
@@ -25106,7 +25144,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>J | 218呎 (开放式)
 $512万
@@ -25114,7 +25152,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K27" s="16" t="inlineStr">
+      <c r="K26" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $720万
@@ -25122,7 +25160,7 @@
 (18年-05月)</t>
         </is>
       </c>
-      <c r="L27" s="16" t="inlineStr">
+      <c r="L26" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $708万
@@ -25130,7 +25168,7 @@
 (18年-05月)</t>
         </is>
       </c>
-      <c r="M27" s="16" t="inlineStr">
+      <c r="M26" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $518万
@@ -25138,7 +25176,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N27" s="16" t="inlineStr">
+      <c r="N26" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $538万
@@ -25146,7 +25184,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O27" s="16" t="inlineStr">
+      <c r="O26" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $950万
@@ -25154,7 +25192,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P27" s="16" t="inlineStr">
+      <c r="P26" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $706万
@@ -25162,7 +25200,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q27" s="16" t="inlineStr">
+      <c r="Q26" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $583万
@@ -25171,13 +25209,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $575万
@@ -25185,7 +25223,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $722万
@@ -25193,7 +25231,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $734万
@@ -25201,7 +25239,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $711万
@@ -25209,7 +25247,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $745万
@@ -25217,15 +25255,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,032万
+$1032万
 $22,886/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $734万
@@ -25233,7 +25271,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $656万
@@ -25241,7 +25279,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $508万
@@ -25249,7 +25287,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K28" s="16" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $715万
@@ -25257,7 +25295,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L28" s="16" t="inlineStr">
+      <c r="L27" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $703万
@@ -25265,7 +25303,7 @@
 (18年-04月)</t>
         </is>
       </c>
-      <c r="M28" s="16" t="inlineStr">
+      <c r="M27" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $514万
@@ -25273,7 +25311,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N28" s="16" t="inlineStr">
+      <c r="N27" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $540万
@@ -25281,7 +25319,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O28" s="16" t="inlineStr">
+      <c r="O27" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $933万
@@ -25289,7 +25327,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P28" s="16" t="inlineStr">
+      <c r="P27" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $705万
@@ -25297,7 +25335,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q28" s="16" t="inlineStr">
+      <c r="Q27" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $583万
@@ -25306,13 +25344,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $569万
@@ -25320,7 +25358,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $706万
@@ -25328,7 +25366,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $719万
@@ -25336,7 +25374,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $706万
@@ -25344,7 +25382,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $740万
@@ -25352,7 +25390,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
 $976万
@@ -25360,7 +25398,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $736万
@@ -25368,7 +25406,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I29" s="16" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $671万
@@ -25376,7 +25414,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J29" s="16" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $504万
@@ -25384,7 +25422,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K29" s="16" t="inlineStr">
+      <c r="K28" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $702万
@@ -25392,7 +25430,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L29" s="16" t="inlineStr">
+      <c r="L28" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $698万
@@ -25400,7 +25438,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M29" s="16" t="inlineStr">
+      <c r="M28" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $527万
@@ -25408,7 +25446,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N29" s="16" t="inlineStr">
+      <c r="N28" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $530万
@@ -25416,7 +25454,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O29" s="16" t="inlineStr">
+      <c r="O28" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $917万
@@ -25424,7 +25462,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P29" s="16" t="inlineStr">
+      <c r="P28" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $697万
@@ -25432,7 +25470,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q29" s="16" t="inlineStr">
+      <c r="Q28" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $570万
@@ -25441,13 +25479,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $567万
@@ -25455,7 +25493,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $711万
@@ -25463,7 +25501,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $723万
@@ -25471,7 +25509,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $711万
@@ -25479,7 +25517,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $737万
@@ -25487,7 +25525,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
 $982万
@@ -25495,7 +25533,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $733万
@@ -25503,7 +25541,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I30" s="16" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $655万
@@ -25511,7 +25549,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $503万
@@ -25519,7 +25557,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K30" s="16" t="inlineStr">
+      <c r="K29" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $727万
@@ -25527,7 +25565,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L30" s="16" t="inlineStr">
+      <c r="L29" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $721万
@@ -25535,7 +25573,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M30" s="16" t="inlineStr">
+      <c r="M29" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $544万
@@ -25543,7 +25581,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N30" s="16" t="inlineStr">
+      <c r="N29" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $538万
@@ -25551,7 +25589,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O30" s="16" t="inlineStr">
+      <c r="O29" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $913万
@@ -25559,7 +25597,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P30" s="16" t="inlineStr">
+      <c r="P29" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $689万
@@ -25567,7 +25605,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q30" s="16" t="inlineStr">
+      <c r="Q29" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $569万
@@ -25576,13 +25614,13 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $576万
@@ -25590,7 +25628,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $708万
@@ -25598,7 +25636,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $721万
@@ -25606,7 +25644,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $701万
@@ -25614,7 +25652,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $750万
@@ -25622,15 +25660,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,009万
+$1009万
 $22,377/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $725万
@@ -25638,7 +25676,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I31" s="16" t="inlineStr">
+      <c r="I30" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $641万
@@ -25646,7 +25684,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J31" s="16" t="inlineStr">
+      <c r="J30" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $502万
@@ -25654,7 +25692,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K31" s="16" t="inlineStr">
+      <c r="K30" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $712万
@@ -25662,7 +25700,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L31" s="16" t="inlineStr">
+      <c r="L30" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $734万
@@ -25670,7 +25708,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M31" s="16" t="inlineStr">
+      <c r="M30" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $527万
@@ -25678,7 +25716,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N31" s="16" t="inlineStr">
+      <c r="N30" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $543万
@@ -25686,7 +25724,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O31" s="16" t="inlineStr">
+      <c r="O30" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $875万
@@ -25694,7 +25732,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P31" s="16" t="inlineStr">
+      <c r="P30" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $680万
@@ -25702,7 +25740,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q31" s="16" t="inlineStr">
+      <c r="Q30" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $557万
@@ -25711,13 +25749,13 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $570万
@@ -25725,7 +25763,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $701万
@@ -25733,7 +25771,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $713万
@@ -25741,7 +25779,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $708万
@@ -25749,7 +25787,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 300呎 (1房)
 $734万
@@ -25757,15 +25795,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
-$1,008万
+$1008万
 $22,352/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $716万
@@ -25773,7 +25811,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I32" s="16" t="inlineStr">
+      <c r="I31" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $640万
@@ -25781,7 +25819,7 @@
 (17年-12月)</t>
         </is>
       </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="J31" s="20" t="inlineStr">
         <is>
           <t>J | 219呎 (开放式)
 $492万
@@ -25789,7 +25827,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K32" s="16" t="inlineStr">
+      <c r="K31" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $718万
@@ -25797,7 +25835,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L32" s="16" t="inlineStr">
+      <c r="L31" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $704万
@@ -25805,7 +25843,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M32" s="16" t="inlineStr">
+      <c r="M31" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $532万
@@ -25813,7 +25851,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N32" s="16" t="inlineStr">
+      <c r="N31" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $532万
@@ -25821,7 +25859,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O32" s="16" t="inlineStr">
+      <c r="O31" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $886万
@@ -25829,7 +25867,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P32" s="16" t="inlineStr">
+      <c r="P31" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $665万
@@ -25837,7 +25875,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q32" s="16" t="inlineStr">
+      <c r="Q31" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $550万
@@ -25846,13 +25884,13 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 234呎 (开放式)
 $579万
@@ -25860,7 +25898,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 290呎 (1房)
 $711万
@@ -25868,7 +25906,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 293呎 (1房)
 $723万
@@ -25876,7 +25914,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 290呎 (1房)
 $703万
@@ -25884,7 +25922,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 299呎 (1房)
 $753万
@@ -25892,7 +25930,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>F | 451呎 (2房)
 $947万
@@ -25900,7 +25938,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>G | 301呎 (1房)
 $708万
@@ -25908,7 +25946,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I33" s="16" t="inlineStr">
+      <c r="I32" s="20" t="inlineStr">
         <is>
           <t>H | 290呎 (1房)
 $626万
@@ -25916,7 +25954,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>J | 218呎 (开放式)
 $486万
@@ -25924,7 +25962,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K33" s="16" t="inlineStr">
+      <c r="K32" s="20" t="inlineStr">
         <is>
           <t>K | 293呎 (1房)
 $689万
@@ -25932,7 +25970,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L33" s="16" t="inlineStr">
+      <c r="L32" s="20" t="inlineStr">
         <is>
           <t>L | 297呎 (1房)
 $717万
@@ -25940,7 +25978,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M33" s="16" t="inlineStr">
+      <c r="M32" s="20" t="inlineStr">
         <is>
           <t>M | 214呎 (开放式)
 $521万
@@ -25948,7 +25986,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N33" s="16" t="inlineStr">
+      <c r="N32" s="20" t="inlineStr">
         <is>
           <t>N | 216呎 (开放式)
 $531万
@@ -25956,7 +25994,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O33" s="16" t="inlineStr">
+      <c r="O32" s="20" t="inlineStr">
         <is>
           <t>P | 384呎 (2房)
 $881万
@@ -25964,7 +26002,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="P33" s="16" t="inlineStr">
+      <c r="P32" s="20" t="inlineStr">
         <is>
           <t>Q | 299呎 (1房)
 $657万
@@ -25972,7 +26010,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q33" s="16" t="inlineStr">
+      <c r="Q32" s="20" t="inlineStr">
         <is>
           <t>R | 238呎 (开放式)
 $543万
@@ -25981,13 +26019,13 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 213呎 (开放式)
 $706万
@@ -25995,7 +26033,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 251呎 (1房)
 $748万
@@ -26003,7 +26041,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 255呎 (1房)
 $770万
@@ -26011,7 +26049,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 252呎 (1房)
 $787万
@@ -26019,7 +26057,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>E | 262呎 (1房)
 $868万
@@ -26027,15 +26065,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>F | 412呎 (2房)
-$1,232万
+$1232万
 $29,904/呎
 (已售)</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>G | 263呎 (1房)
 $817万
@@ -26043,7 +26081,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I34" s="16" t="inlineStr">
+      <c r="I33" s="20" t="inlineStr">
         <is>
           <t>H | 251呎 (1房)
 $768万
@@ -26051,7 +26089,7 @@
 (19年-09月)</t>
         </is>
       </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="J33" s="20" t="inlineStr">
         <is>
           <t>J | 197呎 (开放式)
 $615万
@@ -26059,7 +26097,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="K34" s="16" t="inlineStr">
+      <c r="K33" s="20" t="inlineStr">
         <is>
           <t>K | 255呎 (1房)
 $808万
@@ -26067,7 +26105,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="L34" s="16" t="inlineStr">
+      <c r="L33" s="20" t="inlineStr">
         <is>
           <t>L | 259呎 (1房)
 $815万
@@ -26075,7 +26113,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="M34" s="16" t="inlineStr">
+      <c r="M33" s="20" t="inlineStr">
         <is>
           <t>M | 193呎 (开放式)
 $619万
@@ -26083,7 +26121,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="N34" s="16" t="inlineStr">
+      <c r="N33" s="20" t="inlineStr">
         <is>
           <t>N | 195呎 (开放式)
 $608万
@@ -26091,15 +26129,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="O34" s="16" t="inlineStr">
+      <c r="O33" s="20" t="inlineStr">
         <is>
           <t>P | 344呎 (2房)
-$1,036万
+$1036万
 $30,116/呎
 (已售)</t>
         </is>
       </c>
-      <c r="P34" s="16" t="inlineStr">
+      <c r="P33" s="20" t="inlineStr">
         <is>
           <t>Q | 263呎 (1房)
 $776万
@@ -26107,7 +26145,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="Q34" s="16" t="inlineStr">
+      <c r="Q33" s="20" t="inlineStr">
         <is>
           <t>R | 216呎 (开放式)
 $606万
@@ -26118,7 +26156,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
